--- a/Timesheet-Project/Timesheet 3/Kayden/Kayden_Padayachee_May_FinalWeek.xlsx
+++ b/Timesheet-Project/Timesheet 3/Kayden/Kayden_Padayachee_May_FinalWeek.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_LwazisileMhlambi_2026\Timesheet-Project\Timesheet 3\Kayden\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kpada\OneDrive - ADvTECH Ltd\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="11" documentId="8_{5D82F9B9-C95B-4FD6-8C4D-B31A7BFF422D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C37EABF-7314-4B64-A095-E0C26EC98F9A}"/>
   <bookViews>
-    <workbookView xWindow="2856" yWindow="2856" windowWidth="17280" windowHeight="8880" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
   <sheets>
     <sheet name="May" sheetId="1" r:id="rId1"/>
@@ -856,7 +856,7 @@
     <numFmt numFmtId="166" formatCode="_ [$R-1C09]\ * #,##0.00_ ;_ [$R-1C09]\ * \-#,##0.00_ ;_ [$R-1C09]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="[$R-1C09]#,##0.00;\-[$R-1C09]#,##0.00"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1944,13 +1944,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1966,21 +1981,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2046,6 +2046,147 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="87">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2606,147 +2747,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6758C6CA-2356-4535-9D9D-86230C423211}"/>
@@ -3106,26 +3106,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H76" totalsRowShown="0" headerRowDxfId="86" dataDxfId="85">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H76" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="H2:H76" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H3:H76">
     <sortCondition ref="H64:H76"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="2" xr3:uid="{234A6588-4DEA-4067-9367-AEAFE02CA40D}" name="Resource" dataDxfId="84"/>
+    <tableColumn id="2" xr3:uid="{234A6588-4DEA-4067-9367-AEAFE02CA40D}" name="Resource" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}" name="ProjectTable" displayName="ProjectTable" ref="F2:F40" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82" tableBorderDxfId="81">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}" name="ProjectTable" displayName="ProjectTable" ref="F2:F40" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2" tableBorderDxfId="1">
   <autoFilter ref="F2:F40" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F3:F19">
     <sortCondition ref="F2:F19"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{D9788319-59C4-447A-9364-6F4EF6730453}" name="Description" dataDxfId="80"/>
+    <tableColumn id="1" xr3:uid="{D9788319-59C4-447A-9364-6F4EF6730453}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3402,18 +3402,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451FE93A-CBFB-4D27-9D4A-1E2332DAE6F0}">
   <dimension ref="A5:J81"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.69921875" style="23"/>
+    <col min="8" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.6">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -3423,7 +3423,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="12.6">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -3437,10 +3437,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="12.6">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="25.15">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -3472,7 +3472,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="12.6">
       <c r="A9" s="47">
         <v>46143</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="12.6">
       <c r="A10" s="31">
         <v>46144</v>
       </c>
@@ -3522,7 +3522,7 @@
       <c r="I10" s="35"/>
       <c r="J10" s="35"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="12.6">
       <c r="A11" s="31">
         <v>46145</v>
       </c>
@@ -3541,7 +3541,7 @@
       <c r="I11" s="35"/>
       <c r="J11" s="35"/>
     </row>
-    <row r="12" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="75.75">
       <c r="A12" s="22">
         <v>46146</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>0.53819444444444442</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="37.5">
       <c r="A13" s="22">
         <v>46146</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>0.7104166666666667</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="88.5">
       <c r="A14" s="22">
         <v>46147</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>0.51875000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="50.25">
       <c r="A15" s="22">
         <v>46147</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>0.70972222222222225</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="63">
       <c r="A16" s="22">
         <v>46148</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>0.53472222222222221</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="37.5">
       <c r="A17" s="22">
         <v>46148</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>0.7104166666666667</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="88.5">
       <c r="A18" s="22">
         <v>46149</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="37.5">
       <c r="A19" s="22">
         <v>46149</v>
       </c>
@@ -3788,7 +3788,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="88.5">
       <c r="A20" s="22">
         <v>46150</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="37.5">
       <c r="A21" s="22">
         <v>46150</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>0.70902777777777781</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="31">
         <v>46151</v>
       </c>
@@ -3869,7 +3869,7 @@
       <c r="I22" s="35"/>
       <c r="J22" s="35"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="31">
         <v>46152</v>
       </c>
@@ -3888,7 +3888,7 @@
       <c r="I23" s="35"/>
       <c r="J23" s="35"/>
     </row>
-    <row r="24" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="37.5">
       <c r="A24" s="22">
         <v>46153</v>
       </c>
@@ -3919,7 +3919,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="22">
         <v>46153</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>0.39583333333333331</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="37.5">
       <c r="A26" s="22">
         <v>46153</v>
       </c>
@@ -3979,7 +3979,7 @@
         <v>0.53819444444444442</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="37.5">
       <c r="A27" s="22">
         <v>46153</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>0.71736111111111112</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="88.5">
       <c r="A28" s="22">
         <v>46154</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>0.54305555555555551</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="37.5">
       <c r="A29" s="22">
         <v>46154</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>0.70902777777777781</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="88.5">
       <c r="A30" s="22">
         <v>46155</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>0.53888888888888886</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="50.25">
       <c r="A31" s="22">
         <v>46155</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>0.72152777777777777</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="88.5">
       <c r="A32" s="22">
         <v>46156</v>
       </c>
@@ -4162,7 +4162,7 @@
         <v>0.54027777777777775</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="63">
       <c r="A33" s="22">
         <v>46156</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>0.79722222222222228</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="88.5">
       <c r="A34" s="22">
         <v>46157</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>0.54027777777777775</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="37.5">
       <c r="A35" s="22">
         <v>46157</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>0.71388888888888891</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" s="31">
         <v>46158</v>
       </c>
@@ -4272,7 +4272,7 @@
       <c r="I36" s="35"/>
       <c r="J36" s="35"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37" s="31">
         <v>46159</v>
       </c>
@@ -4291,7 +4291,7 @@
       <c r="I37" s="35"/>
       <c r="J37" s="35"/>
     </row>
-    <row r="38" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="88.5">
       <c r="A38" s="22">
         <v>46160</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>0.53819444444444442</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="37.5">
       <c r="A39" s="22">
         <v>46160</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>0.70902777777777781</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="88.5">
       <c r="A40" s="22">
         <v>46161</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>0.54652777777777772</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="50.25">
       <c r="A41" s="22">
         <v>46161</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>0.71111111111111114</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10">
       <c r="A42" s="22">
         <v>46162</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" ht="88.5">
       <c r="A43" s="22">
         <v>46163</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>0.5395833333333333</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="37.5">
       <c r="A44" s="22">
         <v>46163</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>0.72222222222222221</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" ht="88.5">
       <c r="A45" s="22">
         <v>46164</v>
       </c>
@@ -4539,7 +4539,7 @@
         <v>0.54374999999999996</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="37.5">
       <c r="A46" s="22">
         <v>46164</v>
       </c>
@@ -4570,7 +4570,7 @@
         <v>0.73541666666666672</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10">
       <c r="A47" s="31">
         <v>46165</v>
       </c>
@@ -4589,7 +4589,7 @@
       <c r="I47" s="35"/>
       <c r="J47" s="35"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10">
       <c r="A48" s="31">
         <v>46166</v>
       </c>
@@ -4608,7 +4608,7 @@
       <c r="I48" s="35"/>
       <c r="J48" s="35"/>
     </row>
-    <row r="49" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="75.75">
       <c r="A49" s="22">
         <v>46167</v>
       </c>
@@ -4639,7 +4639,7 @@
         <v>0.54027777777777775</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="25.5">
       <c r="A50" s="22">
         <v>46167</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="25.5">
       <c r="A51" s="22">
         <v>46167</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>0.66597222222222219</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10">
       <c r="A52" s="22">
         <v>46167</v>
       </c>
@@ -4732,7 +4732,7 @@
         <v>0.71944444444444444</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="75.75">
       <c r="A53" s="22">
         <v>46168</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>0.54236111111111107</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" ht="25.5">
       <c r="A54" s="22">
         <v>46168</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="25.5">
       <c r="A55" s="22">
         <v>46168</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="13.9" customHeight="1">
       <c r="A56" s="22">
         <v>46168</v>
       </c>
@@ -4856,7 +4856,7 @@
         <v>0.71250000000000002</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="13.9" customHeight="1">
       <c r="A57" s="22">
         <v>46169</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>0.53680555555555554</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="13.9" customHeight="1">
       <c r="A58" s="22">
         <v>46169</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="13.9" customHeight="1">
       <c r="A59" s="22">
         <v>46169</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="13.9" customHeight="1">
       <c r="A60" s="22">
         <v>46169</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>0.74930555555555556</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="37.5">
       <c r="A61" s="22">
         <v>46170</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="15" customHeight="1">
       <c r="A62" s="22">
         <v>46170</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>0.43888888888888888</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="63">
       <c r="A63" s="22">
         <v>46170</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>0.54097222222222219</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="25.5">
       <c r="A64" s="22">
         <v>46170</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="25.5">
       <c r="A65" s="22">
         <v>46170</v>
       </c>
@@ -5135,7 +5135,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10">
       <c r="A66" s="22">
         <v>46170</v>
       </c>
@@ -5166,7 +5166,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10">
       <c r="A67" s="22">
         <v>46170</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>0.72777777777777775</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="63" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" ht="63">
       <c r="A68" s="22">
         <v>46171</v>
       </c>
@@ -5228,7 +5228,7 @@
         <v>0.54027777777777775</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" ht="37.5">
       <c r="A69" s="22">
         <v>46171</v>
       </c>
@@ -5259,7 +5259,7 @@
         <v>0.73333333333333328</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10">
       <c r="A70" s="31">
         <v>46172</v>
       </c>
@@ -5278,7 +5278,7 @@
       <c r="I70" s="35"/>
       <c r="J70" s="35"/>
     </row>
-    <row r="71" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10">
       <c r="A71" s="31">
         <v>46173</v>
       </c>
@@ -5297,7 +5297,7 @@
       <c r="I71" s="96"/>
       <c r="J71" s="32"/>
     </row>
-    <row r="72" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10">
       <c r="A72" s="46"/>
       <c r="B72" s="45"/>
       <c r="C72" s="45"/>
@@ -5308,7 +5308,7 @@
       <c r="H72" s="36"/>
       <c r="I72" s="37"/>
     </row>
-    <row r="73" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="5"/>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="H73" s="40"/>
     </row>
-    <row r="74" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="9"/>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="H74" s="40"/>
     </row>
-    <row r="75" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="14.25">
       <c r="A75" s="120" t="s">
         <v>60</v>
       </c>
@@ -5345,7 +5345,7 @@
       <c r="F75" s="2"/>
       <c r="H75" s="40"/>
     </row>
-    <row r="76" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="14.25">
       <c r="A76" s="13"/>
       <c r="B76" s="13"/>
       <c r="C76" s="6"/>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="H76" s="38"/>
     </row>
-    <row r="77" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ht="14.25">
       <c r="A77" s="121" t="s">
         <v>62</v>
       </c>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="H77" s="40"/>
     </row>
-    <row r="78" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="14.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="H78" s="40"/>
     </row>
-    <row r="79" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -5398,7 +5398,7 @@
       <c r="F79" s="2"/>
       <c r="H79" s="40"/>
     </row>
-    <row r="80" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -5409,7 +5409,7 @@
       <c r="F80" s="21"/>
       <c r="H80" s="40"/>
     </row>
-    <row r="81" spans="5:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="5:8">
       <c r="E81" s="39"/>
       <c r="H81" s="40"/>
     </row>
@@ -5420,56 +5420,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="79" priority="21" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="86" priority="21" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="22" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="85" priority="22" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="77" priority="23" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="84" priority="23" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="24" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="83" priority="24" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="25" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="82" priority="25" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="74" priority="26" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="81" priority="26" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="27" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B81">
-    <cfRule type="containsText" dxfId="72" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="79" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="71" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="78" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D71:E73 D75:E77 E80">
-    <cfRule type="containsText" dxfId="70" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="77" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D71)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="69" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="76" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D71)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="75" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D71)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="67" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="74" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D71)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="73" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D71)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="65" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="72" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D71)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5521,18 +5521,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738C92ED-F226-4107-8C14-FCA383B998C3}">
   <dimension ref="A5:J48"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.69921875" style="23"/>
+    <col min="8" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -5542,7 +5542,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -5556,10 +5556,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="25.15">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -5591,7 +5591,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="22">
         <v>46174</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="22">
         <v>46175</v>
       </c>
@@ -5643,7 +5643,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="22">
         <v>46176</v>
       </c>
@@ -5662,7 +5662,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="22">
         <v>46177</v>
       </c>
@@ -5681,7 +5681,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="22">
         <v>46178</v>
       </c>
@@ -5700,7 +5700,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="31">
         <v>46179</v>
       </c>
@@ -5719,7 +5719,7 @@
       <c r="I14" s="35"/>
       <c r="J14" s="35"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="31">
         <v>46180</v>
       </c>
@@ -5738,7 +5738,7 @@
       <c r="I15" s="35"/>
       <c r="J15" s="35"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="22">
         <v>46181</v>
       </c>
@@ -5757,7 +5757,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="22">
         <v>46182</v>
       </c>
@@ -5776,7 +5776,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="22">
         <v>46183</v>
       </c>
@@ -5795,7 +5795,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="22">
         <v>46184</v>
       </c>
@@ -5814,7 +5814,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="22">
         <v>46185</v>
       </c>
@@ -5833,7 +5833,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="31">
         <v>46186</v>
       </c>
@@ -5852,7 +5852,7 @@
       <c r="I21" s="35"/>
       <c r="J21" s="35"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="31">
         <v>46187</v>
       </c>
@@ -5871,7 +5871,7 @@
       <c r="I22" s="35"/>
       <c r="J22" s="35"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="22">
         <v>46188</v>
       </c>
@@ -5890,7 +5890,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="47">
         <v>46189</v>
       </c>
@@ -5921,7 +5921,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="22">
         <v>46190</v>
       </c>
@@ -5940,7 +5940,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="22">
         <v>46191</v>
       </c>
@@ -5959,7 +5959,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="22">
         <v>46192</v>
       </c>
@@ -5978,7 +5978,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="31">
         <v>46193</v>
       </c>
@@ -5997,7 +5997,7 @@
       <c r="I28" s="35"/>
       <c r="J28" s="35"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="31">
         <v>46194</v>
       </c>
@@ -6016,7 +6016,7 @@
       <c r="I29" s="35"/>
       <c r="J29" s="35"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="22">
         <v>46195</v>
       </c>
@@ -6035,7 +6035,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" s="22">
         <v>46196</v>
       </c>
@@ -6054,7 +6054,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="22">
         <v>46197</v>
       </c>
@@ -6073,7 +6073,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="22">
         <v>46198</v>
       </c>
@@ -6092,7 +6092,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="22">
         <v>46199</v>
       </c>
@@ -6111,7 +6111,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" s="31">
         <v>46200</v>
       </c>
@@ -6130,7 +6130,7 @@
       <c r="I35" s="35"/>
       <c r="J35" s="35"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" s="31">
         <v>46201</v>
       </c>
@@ -6149,7 +6149,7 @@
       <c r="I36" s="35"/>
       <c r="J36" s="35"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37" s="22">
         <v>46202</v>
       </c>
@@ -6168,7 +6168,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="13.15" thickBot="1">
       <c r="A38" s="22">
         <v>46203</v>
       </c>
@@ -6187,7 +6187,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A39" s="45"/>
       <c r="B39" s="45"/>
       <c r="C39" s="45"/>
@@ -6198,7 +6198,7 @@
       <c r="H39" s="36"/>
       <c r="I39" s="37"/>
     </row>
-    <row r="40" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="13.9" customHeight="1">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="H40" s="40"/>
     </row>
-    <row r="41" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="9"/>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A42" s="120" t="s">
         <v>60</v>
       </c>
@@ -6235,7 +6235,7 @@
       <c r="F42" s="2"/>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="13.9">
       <c r="A43" s="13"/>
       <c r="B43" s="13"/>
       <c r="C43" s="6"/>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="H43" s="38"/>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A44" s="121" t="s">
         <v>62</v>
       </c>
@@ -6265,7 +6265,7 @@
       </c>
       <c r="H44" s="40"/>
     </row>
-    <row r="45" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="14.45" thickBot="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="13.9" thickBot="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -6288,7 +6288,7 @@
       <c r="F46" s="2"/>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="13.9" thickBot="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -6299,7 +6299,7 @@
       <c r="F47" s="21"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="13.15" thickBot="1">
       <c r="E48" s="39"/>
       <c r="H48" s="40"/>
     </row>
@@ -6310,56 +6310,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="63" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="70" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="69" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="61" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="68" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="67" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="66" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="65" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B48">
-    <cfRule type="containsText" dxfId="56" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="63" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="55" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="62" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39:E40 D42:E44 E47">
-    <cfRule type="containsText" dxfId="54" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="61" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="53" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="60" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="59" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="58" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="57" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="56" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6417,18 +6417,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4077AC14-6A48-4DDF-A891-D5BFFE7E5F3C}">
   <dimension ref="A5:J49"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.69921875" style="23"/>
+    <col min="8" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -6438,7 +6438,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -6452,10 +6452,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="25.15">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -6487,7 +6487,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="22">
         <v>46204</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="22">
         <v>46205</v>
       </c>
@@ -6539,7 +6539,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="22">
         <v>46206</v>
       </c>
@@ -6558,7 +6558,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="31">
         <v>46207</v>
       </c>
@@ -6577,7 +6577,7 @@
       <c r="I12" s="35"/>
       <c r="J12" s="35"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="31">
         <v>46208</v>
       </c>
@@ -6596,7 +6596,7 @@
       <c r="I13" s="35"/>
       <c r="J13" s="35"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="22">
         <v>46209</v>
       </c>
@@ -6615,7 +6615,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="22">
         <v>46210</v>
       </c>
@@ -6634,7 +6634,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="22">
         <v>46211</v>
       </c>
@@ -6653,7 +6653,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="22">
         <v>46212</v>
       </c>
@@ -6672,7 +6672,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="22">
         <v>46213</v>
       </c>
@@ -6691,7 +6691,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="31">
         <v>46214</v>
       </c>
@@ -6710,7 +6710,7 @@
       <c r="I19" s="35"/>
       <c r="J19" s="35"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="31">
         <v>46215</v>
       </c>
@@ -6729,7 +6729,7 @@
       <c r="I20" s="35"/>
       <c r="J20" s="35"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="22">
         <v>46216</v>
       </c>
@@ -6748,7 +6748,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="22">
         <v>46217</v>
       </c>
@@ -6767,7 +6767,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="22">
         <v>46218</v>
       </c>
@@ -6786,7 +6786,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="22">
         <v>46219</v>
       </c>
@@ -6805,7 +6805,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="22">
         <v>46220</v>
       </c>
@@ -6824,7 +6824,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="31">
         <v>46221</v>
       </c>
@@ -6843,7 +6843,7 @@
       <c r="I26" s="35"/>
       <c r="J26" s="35"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="31">
         <v>46222</v>
       </c>
@@ -6862,7 +6862,7 @@
       <c r="I27" s="35"/>
       <c r="J27" s="35"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="22">
         <v>46223</v>
       </c>
@@ -6881,7 +6881,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="22">
         <v>46224</v>
       </c>
@@ -6900,7 +6900,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="22">
         <v>46225</v>
       </c>
@@ -6919,7 +6919,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" s="22">
         <v>46226</v>
       </c>
@@ -6938,7 +6938,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="22">
         <v>46227</v>
       </c>
@@ -6957,7 +6957,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="31">
         <v>46228</v>
       </c>
@@ -6976,7 +6976,7 @@
       <c r="I33" s="35"/>
       <c r="J33" s="35"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="31">
         <v>46229</v>
       </c>
@@ -6995,7 +6995,7 @@
       <c r="I34" s="35"/>
       <c r="J34" s="35"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" s="22">
         <v>46230</v>
       </c>
@@ -7014,7 +7014,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" s="22">
         <v>46231</v>
       </c>
@@ -7033,7 +7033,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37" s="22">
         <v>46232</v>
       </c>
@@ -7052,7 +7052,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38" s="22">
         <v>46233</v>
       </c>
@@ -7071,7 +7071,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="13.15" thickBot="1">
       <c r="A39" s="22">
         <v>46234</v>
       </c>
@@ -7090,7 +7090,7 @@
       <c r="I39" s="30"/>
       <c r="J39" s="30"/>
     </row>
-    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A40" s="3"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -7101,7 +7101,7 @@
       <c r="H40" s="36"/>
       <c r="I40" s="37"/>
     </row>
-    <row r="41" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="13.9" customHeight="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="9"/>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A43" s="120" t="s">
         <v>60</v>
       </c>
@@ -7138,7 +7138,7 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="13.9">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A45" s="121" t="s">
         <v>62</v>
       </c>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="14.45" thickBot="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="13.9" thickBot="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -7191,7 +7191,7 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="13.9" thickBot="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -7202,7 +7202,7 @@
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:8" ht="13.15" thickBot="1">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -7213,56 +7213,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="47" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="54" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="53" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="45" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="52" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="51" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="50" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="49" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B49">
-    <cfRule type="containsText" dxfId="40" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="47" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="39" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="46" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E41 D43:E45 E48">
-    <cfRule type="containsText" dxfId="38" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="45" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="44" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="43" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="42" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="41" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="40" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7324,18 +7324,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F5FF808-4CDC-4429-9978-CAD26FE6591A}">
   <dimension ref="A5:J49"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.69921875" style="23"/>
+    <col min="8" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -7345,7 +7345,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -7359,10 +7359,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="25.15">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -7394,7 +7394,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="31">
         <v>46235</v>
       </c>
@@ -7413,7 +7413,7 @@
       <c r="I9" s="35"/>
       <c r="J9" s="35"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="31">
         <v>46236</v>
       </c>
@@ -7432,7 +7432,7 @@
       <c r="I10" s="35"/>
       <c r="J10" s="35"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="22">
         <v>46237</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="22">
         <v>46238</v>
       </c>
@@ -7484,7 +7484,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="22">
         <v>46239</v>
       </c>
@@ -7503,7 +7503,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="22">
         <v>46240</v>
       </c>
@@ -7522,7 +7522,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="22">
         <v>46241</v>
       </c>
@@ -7541,7 +7541,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="31">
         <v>46242</v>
       </c>
@@ -7560,7 +7560,7 @@
       <c r="I16" s="35"/>
       <c r="J16" s="35"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="31">
         <v>46243</v>
       </c>
@@ -7581,7 +7581,7 @@
       <c r="I17" s="35"/>
       <c r="J17" s="35"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="47">
         <v>46244</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="22">
         <v>46245</v>
       </c>
@@ -7631,7 +7631,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="22">
         <v>46246</v>
       </c>
@@ -7650,7 +7650,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="22">
         <v>46247</v>
       </c>
@@ -7669,7 +7669,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="22">
         <v>46248</v>
       </c>
@@ -7688,7 +7688,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="31">
         <v>46249</v>
       </c>
@@ -7707,7 +7707,7 @@
       <c r="I23" s="35"/>
       <c r="J23" s="35"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="31">
         <v>46250</v>
       </c>
@@ -7726,7 +7726,7 @@
       <c r="I24" s="35"/>
       <c r="J24" s="35"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="22">
         <v>46251</v>
       </c>
@@ -7745,7 +7745,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="22">
         <v>46252</v>
       </c>
@@ -7764,7 +7764,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="22">
         <v>46253</v>
       </c>
@@ -7783,7 +7783,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="22">
         <v>46254</v>
       </c>
@@ -7802,7 +7802,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="22">
         <v>46255</v>
       </c>
@@ -7821,7 +7821,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="31">
         <v>46256</v>
       </c>
@@ -7840,7 +7840,7 @@
       <c r="I30" s="35"/>
       <c r="J30" s="35"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" s="31">
         <v>46257</v>
       </c>
@@ -7859,7 +7859,7 @@
       <c r="I31" s="35"/>
       <c r="J31" s="35"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="22">
         <v>46258</v>
       </c>
@@ -7878,7 +7878,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="22">
         <v>46259</v>
       </c>
@@ -7897,7 +7897,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="22">
         <v>46260</v>
       </c>
@@ -7916,7 +7916,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" s="22">
         <v>46261</v>
       </c>
@@ -7935,7 +7935,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" s="22">
         <v>46262</v>
       </c>
@@ -7954,7 +7954,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37" s="31">
         <v>46263</v>
       </c>
@@ -7973,7 +7973,7 @@
       <c r="I37" s="35"/>
       <c r="J37" s="35"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38" s="31">
         <v>46264</v>
       </c>
@@ -7992,7 +7992,7 @@
       <c r="I38" s="35"/>
       <c r="J38" s="35"/>
     </row>
-    <row r="39" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="13.9" customHeight="1">
       <c r="A39" s="22">
         <v>46265</v>
       </c>
@@ -8011,7 +8011,7 @@
       <c r="I39" s="30"/>
       <c r="J39" s="30"/>
     </row>
-    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A40" s="46"/>
       <c r="B40" s="45"/>
       <c r="C40" s="45"/>
@@ -8022,7 +8022,7 @@
       <c r="H40" s="36"/>
       <c r="I40" s="37"/>
     </row>
-    <row r="41" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="13.9" customHeight="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="9"/>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A43" s="120" t="s">
         <v>60</v>
       </c>
@@ -8059,7 +8059,7 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="13.9">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A45" s="121" t="s">
         <v>62</v>
       </c>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="14.45" thickBot="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="13.9" thickBot="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -8112,7 +8112,7 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="13.9" thickBot="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -8123,7 +8123,7 @@
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:8" ht="13.15" thickBot="1">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -8134,56 +8134,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="31" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="38" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="37" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="29" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="36" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="35" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="34" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="33" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B49">
-    <cfRule type="containsText" dxfId="24" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="30" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E41 D43:E45 E48">
-    <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="28" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="27" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="26" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="24" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8235,18 +8235,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D1366D5-46F5-410C-BC9F-D56DCF566D28}">
   <dimension ref="A5:J48"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.69921875" style="23"/>
+    <col min="8" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -8256,7 +8256,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -8270,10 +8270,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="25.15">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -8305,7 +8305,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="22">
         <v>46266</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="22">
         <v>46267</v>
       </c>
@@ -8357,7 +8357,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="22">
         <v>46268</v>
       </c>
@@ -8376,7 +8376,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="22">
         <v>46269</v>
       </c>
@@ -8395,7 +8395,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="31">
         <v>46270</v>
       </c>
@@ -8414,7 +8414,7 @@
       <c r="I13" s="35"/>
       <c r="J13" s="35"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="31">
         <v>46271</v>
       </c>
@@ -8433,7 +8433,7 @@
       <c r="I14" s="35"/>
       <c r="J14" s="35"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="22">
         <v>46272</v>
       </c>
@@ -8452,7 +8452,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="22">
         <v>46273</v>
       </c>
@@ -8471,7 +8471,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="22">
         <v>46274</v>
       </c>
@@ -8490,7 +8490,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="22">
         <v>46275</v>
       </c>
@@ -8509,7 +8509,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="22">
         <v>46276</v>
       </c>
@@ -8528,7 +8528,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="31">
         <v>46277</v>
       </c>
@@ -8547,7 +8547,7 @@
       <c r="I20" s="35"/>
       <c r="J20" s="35"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="31">
         <v>46278</v>
       </c>
@@ -8566,7 +8566,7 @@
       <c r="I21" s="35"/>
       <c r="J21" s="35"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="22">
         <v>46279</v>
       </c>
@@ -8585,7 +8585,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="22">
         <v>46280</v>
       </c>
@@ -8604,7 +8604,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="22">
         <v>46281</v>
       </c>
@@ -8623,7 +8623,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="22">
         <v>46282</v>
       </c>
@@ -8642,7 +8642,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="22">
         <v>46283</v>
       </c>
@@ -8661,7 +8661,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="31">
         <v>46284</v>
       </c>
@@ -8680,7 +8680,7 @@
       <c r="I27" s="35"/>
       <c r="J27" s="35"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="31">
         <v>46285</v>
       </c>
@@ -8699,7 +8699,7 @@
       <c r="I28" s="35"/>
       <c r="J28" s="35"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="22">
         <v>46286</v>
       </c>
@@ -8718,7 +8718,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="22">
         <v>46287</v>
       </c>
@@ -8737,7 +8737,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" s="22">
         <v>46288</v>
       </c>
@@ -8756,7 +8756,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="47">
         <v>46289</v>
       </c>
@@ -8787,7 +8787,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="22">
         <v>46290</v>
       </c>
@@ -8806,7 +8806,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="31">
         <v>46291</v>
       </c>
@@ -8825,7 +8825,7 @@
       <c r="I34" s="35"/>
       <c r="J34" s="35"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" s="31">
         <v>46292</v>
       </c>
@@ -8844,7 +8844,7 @@
       <c r="I35" s="35"/>
       <c r="J35" s="35"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" s="22">
         <v>46293</v>
       </c>
@@ -8863,7 +8863,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37" s="22">
         <v>46294</v>
       </c>
@@ -8882,7 +8882,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38" s="22">
         <v>46295</v>
       </c>
@@ -8901,7 +8901,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A39" s="46"/>
       <c r="B39" s="46"/>
       <c r="C39" s="45"/>
@@ -8912,7 +8912,7 @@
       <c r="H39" s="36"/>
       <c r="I39" s="37"/>
     </row>
-    <row r="40" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="13.9" customHeight="1">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="H40" s="40"/>
     </row>
-    <row r="41" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="9"/>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A42" s="120" t="s">
         <v>60</v>
       </c>
@@ -8949,7 +8949,7 @@
       <c r="F42" s="2"/>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="13.9">
       <c r="A43" s="13"/>
       <c r="B43" s="13"/>
       <c r="C43" s="6"/>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="H43" s="38"/>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A44" s="121" t="s">
         <v>62</v>
       </c>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="H44" s="40"/>
     </row>
-    <row r="45" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="14.45" thickBot="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -8993,7 +8993,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="13.9" thickBot="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -9002,7 +9002,7 @@
       <c r="F46" s="2"/>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="13.9" thickBot="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -9013,7 +9013,7 @@
       <c r="F47" s="21"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="13.15" thickBot="1">
       <c r="E48" s="39"/>
       <c r="H48" s="40"/>
     </row>
@@ -9024,56 +9024,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7 D39:E40">
-    <cfRule type="containsText" dxfId="15" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="22" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="21" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="20" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="18" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="17" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B48">
-    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="15" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="14" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42:E44 E47">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9141,18 +9141,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{368E8809-782A-4EC8-A7EE-23E6EB29126F}">
   <dimension ref="A1:O18"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.69921875" style="23"/>
-    <col min="5" max="5" width="13.19921875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.75" style="23"/>
+    <col min="5" max="5" width="13.25" style="23" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="23" customWidth="1"/>
-    <col min="7" max="16384" width="8.69921875" style="23"/>
+    <col min="7" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="13.5" customHeight="1">
       <c r="A1" s="78"/>
       <c r="B1" s="78"/>
       <c r="C1" s="78"/>
@@ -9160,7 +9160,7 @@
       <c r="E1" s="78"/>
       <c r="F1" s="78"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
       <c r="C2" s="82"/>
@@ -9168,7 +9168,7 @@
       <c r="E2" s="82"/>
       <c r="F2" s="82"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15">
       <c r="A3" s="77"/>
       <c r="B3" s="77"/>
       <c r="C3" s="83"/>
@@ -9176,7 +9176,7 @@
       <c r="E3" s="83"/>
       <c r="F3" s="83"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15">
       <c r="A4" s="77"/>
       <c r="B4" s="77"/>
       <c r="C4" s="84"/>
@@ -9184,7 +9184,7 @@
       <c r="E4" s="84"/>
       <c r="F4" s="84"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -9196,7 +9196,7 @@
       <c r="E5" s="84"/>
       <c r="F5" s="84"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15">
       <c r="A6" s="77" t="s">
         <v>74</v>
       </c>
@@ -9209,7 +9209,7 @@
       <c r="E6" s="83"/>
       <c r="F6" s="83"/>
     </row>
-    <row r="7" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="13.5" customHeight="1">
       <c r="A7" s="71"/>
       <c r="B7" s="72"/>
       <c r="C7" s="72"/>
@@ -9217,139 +9217,139 @@
       <c r="E7" s="83"/>
       <c r="F7" s="83"/>
     </row>
-    <row r="8" spans="1:15" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="130" t="s">
+    <row r="8" spans="1:15" ht="27.4" customHeight="1">
+      <c r="A8" s="127" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="130"/>
-      <c r="C8" s="130"/>
-      <c r="D8" s="130"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="130"/>
-    </row>
-    <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+    </row>
+    <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1">
       <c r="A9" s="80" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="133" t="s">
+      <c r="B9" s="124" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="134"/>
-      <c r="D9" s="133" t="s">
+      <c r="C9" s="125"/>
+      <c r="D9" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="E9" s="134"/>
+      <c r="E9" s="125"/>
       <c r="F9" s="81" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15">
       <c r="A10" s="76">
         <v>46113</v>
       </c>
-      <c r="B10" s="124" t="s">
+      <c r="B10" s="126" t="s">
         <v>80</v>
       </c>
-      <c r="C10" s="124"/>
-      <c r="D10" s="124" t="s">
+      <c r="C10" s="126"/>
+      <c r="D10" s="126" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="124"/>
+      <c r="E10" s="126"/>
       <c r="F10" s="75">
         <v>200</v>
       </c>
-      <c r="G10" s="131" t="s">
+      <c r="G10" s="122" t="s">
         <v>82</v>
       </c>
-      <c r="H10" s="132"/>
-      <c r="I10" s="132"/>
-      <c r="J10" s="132"/>
-      <c r="K10" s="132"/>
-      <c r="L10" s="132"/>
-      <c r="M10" s="132"/>
-      <c r="N10" s="132"/>
-      <c r="O10" s="132"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="H10" s="123"/>
+      <c r="I10" s="123"/>
+      <c r="J10" s="123"/>
+      <c r="K10" s="123"/>
+      <c r="L10" s="123"/>
+      <c r="M10" s="123"/>
+      <c r="N10" s="123"/>
+      <c r="O10" s="123"/>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="76">
         <v>46113</v>
       </c>
-      <c r="B11" s="122" t="s">
+      <c r="B11" s="128" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="123"/>
-      <c r="D11" s="124" t="s">
+      <c r="C11" s="129"/>
+      <c r="D11" s="126" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="124"/>
+      <c r="E11" s="126"/>
       <c r="F11" s="75"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15">
       <c r="A12" s="76">
         <v>46113</v>
       </c>
-      <c r="B12" s="122" t="s">
+      <c r="B12" s="128" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="123"/>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="126"/>
+      <c r="E12" s="126"/>
       <c r="F12" s="75"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15">
       <c r="A13" s="76">
         <v>46113</v>
       </c>
-      <c r="B13" s="122"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="124"/>
-      <c r="E13" s="124"/>
+      <c r="B13" s="128"/>
+      <c r="C13" s="129"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
       <c r="F13" s="75"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15">
       <c r="A14" s="76">
         <v>46113</v>
       </c>
-      <c r="B14" s="122"/>
-      <c r="C14" s="123"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124"/>
+      <c r="B14" s="128"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="126"/>
+      <c r="E14" s="126"/>
       <c r="F14" s="75"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15">
       <c r="A15" s="76">
         <v>46113</v>
       </c>
-      <c r="B15" s="128"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="124"/>
-      <c r="E15" s="124"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="126"/>
       <c r="F15" s="75"/>
     </row>
-    <row r="16" spans="1:15" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="13.15" thickBot="1">
       <c r="A16" s="76">
         <v>46113</v>
       </c>
-      <c r="B16" s="122"/>
-      <c r="C16" s="123"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="124"/>
+      <c r="B16" s="128"/>
+      <c r="C16" s="129"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="126"/>
       <c r="F16" s="75"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="125" t="s">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A17" s="130" t="s">
         <v>86</v>
       </c>
-      <c r="B17" s="126"/>
-      <c r="C17" s="126"/>
-      <c r="D17" s="126"/>
-      <c r="E17" s="127"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="132"/>
       <c r="F17" s="74">
         <f>SUM(F10:F16)</f>
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" s="71"/>
       <c r="B18" s="72"/>
       <c r="C18" s="72"/>
@@ -9359,16 +9359,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -9378,6 +9368,16 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -9407,19 +9407,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0517D5F3-AC91-43ED-96BB-0299CBED5EE0}">
   <dimension ref="A4:F23"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="15.5" style="23" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" style="23" customWidth="1"/>
-    <col min="3" max="3" width="9.69921875" style="23" customWidth="1"/>
-    <col min="4" max="16384" width="8.69921875" style="23"/>
+    <col min="3" max="3" width="9.75" style="23" customWidth="1"/>
+    <col min="4" max="16384" width="8.75" style="23"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" s="135"/>
       <c r="B4" s="135"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -9427,7 +9427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" s="77" t="s">
         <v>87</v>
       </c>
@@ -9435,7 +9435,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" s="93" t="s">
         <v>89</v>
       </c>
@@ -9443,11 +9443,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" s="94"/>
       <c r="B8" s="83"/>
     </row>
-    <row r="9" spans="1:6" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="27.4" customHeight="1">
       <c r="A9" s="150" t="s">
         <v>91</v>
       </c>
@@ -9457,7 +9457,7 @@
       <c r="E9" s="150"/>
       <c r="F9" s="150"/>
     </row>
-    <row r="10" spans="1:6" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="25.15">
       <c r="A10" s="85" t="s">
         <v>92</v>
       </c>
@@ -9477,7 +9477,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" s="85" t="s">
         <v>41</v>
       </c>
@@ -9495,7 +9495,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" s="85"/>
       <c r="B12" s="85"/>
       <c r="C12" s="85"/>
@@ -9503,7 +9503,7 @@
       <c r="E12" s="85"/>
       <c r="F12" s="85"/>
     </row>
-    <row r="13" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.15" thickBot="1">
       <c r="A13" s="85"/>
       <c r="B13" s="85"/>
       <c r="C13" s="85"/>
@@ -9511,7 +9511,7 @@
       <c r="E13" s="85"/>
       <c r="F13" s="85"/>
     </row>
-    <row r="14" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.15" thickBot="1">
       <c r="A14" s="86"/>
       <c r="B14" s="87"/>
       <c r="C14" s="87"/>
@@ -9522,7 +9522,7 @@
       <c r="E14" s="87"/>
       <c r="F14" s="89"/>
     </row>
-    <row r="15" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.15" thickBot="1">
       <c r="A15" s="140"/>
       <c r="B15" s="141"/>
       <c r="C15" s="141"/>
@@ -9530,7 +9530,7 @@
       <c r="E15" s="141"/>
       <c r="F15" s="141"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" s="151" t="s">
         <v>99</v>
       </c>
@@ -9540,7 +9540,7 @@
       <c r="E16" s="152"/>
       <c r="F16" s="153"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" s="136" t="s">
         <v>100</v>
       </c>
@@ -9550,7 +9550,7 @@
       <c r="E17" s="137"/>
       <c r="F17" s="138"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" s="139"/>
       <c r="B18" s="137"/>
       <c r="C18" s="137"/>
@@ -9558,7 +9558,7 @@
       <c r="E18" s="137"/>
       <c r="F18" s="138"/>
     </row>
-    <row r="19" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.15" thickBot="1">
       <c r="A19" s="140"/>
       <c r="B19" s="141"/>
       <c r="C19" s="141"/>
@@ -9566,8 +9566,8 @@
       <c r="E19" s="141"/>
       <c r="F19" s="142"/>
     </row>
-    <row r="20" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="13.15" thickBot="1"/>
+    <row r="21" spans="1:6">
       <c r="A21" s="90" t="s">
         <v>3</v>
       </c>
@@ -9579,7 +9579,7 @@
       <c r="E21" s="144"/>
       <c r="F21" s="145"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" s="91" t="s">
         <v>101</v>
       </c>
@@ -9591,7 +9591,7 @@
       <c r="E22" s="146"/>
       <c r="F22" s="147"/>
     </row>
-    <row r="23" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.15" thickBot="1">
       <c r="A23" s="92" t="s">
         <v>103</v>
       </c>
@@ -9658,18 +9658,18 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="B2:J76"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="8.69921875" style="52"/>
+    <col min="1" max="1" width="8.75" style="52"/>
     <col min="2" max="2" width="25.5" style="52" customWidth="1"/>
-    <col min="3" max="3" width="8.69921875" style="52"/>
-    <col min="4" max="4" width="19.19921875" style="52" customWidth="1"/>
-    <col min="5" max="5" width="8.69921875" style="52"/>
-    <col min="6" max="6" width="21.69921875" style="52" customWidth="1"/>
-    <col min="7" max="16384" width="8.69921875" style="52"/>
+    <col min="3" max="3" width="8.75" style="52"/>
+    <col min="4" max="4" width="19.25" style="52" customWidth="1"/>
+    <col min="5" max="5" width="8.75" style="52"/>
+    <col min="6" max="6" width="21.75" style="52" customWidth="1"/>
+    <col min="7" max="16384" width="8.75" style="52"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" ht="15" thickBot="1">
       <c r="B2" s="64" t="s">
         <v>14</v>
       </c>
@@ -9686,7 +9686,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10">
       <c r="B3" s="64" t="s">
         <v>106</v>
       </c>
@@ -9704,7 +9704,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10">
       <c r="B4" s="64" t="s">
         <v>109</v>
       </c>
@@ -9722,7 +9722,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10">
       <c r="B5" s="64" t="s">
         <v>113</v>
       </c>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I5" s="98"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10">
       <c r="B6" s="64" t="s">
         <v>117</v>
       </c>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="I6" s="99"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10">
       <c r="B7" s="64" t="s">
         <v>121</v>
       </c>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="I7" s="100"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10">
       <c r="B8" s="64" t="s">
         <v>124</v>
       </c>
@@ -9785,7 +9785,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10">
       <c r="B9" s="64" t="s">
         <v>129</v>
       </c>
@@ -9803,7 +9803,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10">
       <c r="B10" s="64" t="s">
         <v>133</v>
       </c>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="I10" s="100"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10">
       <c r="B11" s="64" t="s">
         <v>137</v>
       </c>
@@ -9836,7 +9836,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10">
       <c r="B12" s="64" t="s">
         <v>142</v>
       </c>
@@ -9851,7 +9851,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10">
       <c r="B13" s="64" t="s">
         <v>146</v>
       </c>
@@ -9863,7 +9863,7 @@
       </c>
       <c r="I13" s="101"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10">
       <c r="B14" s="64" t="s">
         <v>149</v>
       </c>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="I14" s="102"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10">
       <c r="B15" s="64" t="s">
         <v>152</v>
       </c>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="I15" s="101"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10">
       <c r="B16" s="64" t="s">
         <v>155</v>
       </c>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="I16" s="103"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9">
       <c r="B17" s="64" t="s">
         <v>158</v>
       </c>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="I17" s="101"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9">
       <c r="B18" s="64" t="s">
         <v>161</v>
       </c>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="I18" s="103"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9">
       <c r="B19" s="64" t="s">
         <v>164</v>
       </c>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="I19" s="104"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9">
       <c r="B20" s="64" t="s">
         <v>166</v>
       </c>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="I20" s="102"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9">
       <c r="B21" s="64" t="s">
         <v>169</v>
       </c>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="I21" s="100"/>
     </row>
-    <row r="22" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" ht="27.6">
       <c r="B22" s="64" t="s">
         <v>172</v>
       </c>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="I22" s="105"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9">
       <c r="B23" s="64" t="s">
         <v>175</v>
       </c>
@@ -9993,7 +9993,7 @@
       </c>
       <c r="I23" s="106"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9">
       <c r="B24" s="64" t="s">
         <v>177</v>
       </c>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="I24" s="107"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9">
       <c r="B25" s="64" t="s">
         <v>180</v>
       </c>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="I25" s="108"/>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9">
       <c r="B26" s="64" t="s">
         <v>183</v>
       </c>
@@ -10030,7 +10030,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9">
       <c r="B27" s="64" t="s">
         <v>186</v>
       </c>
@@ -10043,7 +10043,7 @@
       </c>
       <c r="I27" s="106"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9">
       <c r="B28" s="64" t="s">
         <v>189</v>
       </c>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="I28" s="68"/>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9">
       <c r="B29" s="64" t="s">
         <v>192</v>
       </c>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="I29" s="109"/>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9">
       <c r="B30" s="64" t="s">
         <v>195</v>
       </c>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="107"/>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:9">
       <c r="B31" s="64" t="s">
         <v>198</v>
       </c>
@@ -10091,7 +10091,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:9">
       <c r="B32" s="64" t="s">
         <v>201</v>
       </c>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="I32" s="108"/>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:9">
       <c r="B33" s="64" t="s">
         <v>204</v>
       </c>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="I33" s="108"/>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:9">
       <c r="B34" s="64" t="s">
         <v>206</v>
       </c>
@@ -10127,7 +10127,7 @@
       </c>
       <c r="I34" s="67"/>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:9">
       <c r="B35" s="64" t="s">
         <v>208</v>
       </c>
@@ -10139,7 +10139,7 @@
       </c>
       <c r="I35" s="107"/>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:9">
       <c r="B36" s="64" t="s">
         <v>211</v>
       </c>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="I36" s="100"/>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:9">
       <c r="B37" s="64" t="s">
         <v>214</v>
       </c>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="I37" s="108"/>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:9">
       <c r="B38" s="64" t="s">
         <v>217</v>
       </c>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="I38" s="107"/>
     </row>
-    <row r="39" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:9" ht="27.6">
       <c r="B39" s="64" t="s">
         <v>219</v>
       </c>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="I39" s="109"/>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:9">
       <c r="B40" s="64" t="s">
         <v>222</v>
       </c>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="I40" s="110"/>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:9">
       <c r="B41" s="64" t="s">
         <v>225</v>
       </c>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="I41" s="110"/>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:9">
       <c r="B42" s="64" t="s">
         <v>227</v>
       </c>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="I42" s="107"/>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:9">
       <c r="B43" s="64" t="s">
         <v>229</v>
       </c>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="I43" s="109"/>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:9">
       <c r="B44" s="119" t="s">
         <v>231</v>
       </c>
@@ -10235,158 +10235,158 @@
         <v>232</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:9">
       <c r="H45" s="110" t="s">
         <v>233</v>
       </c>
       <c r="I45" s="108"/>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:9">
       <c r="H46" s="68" t="s">
         <v>234</v>
       </c>
       <c r="I46" s="111"/>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:9">
       <c r="B47" s="62"/>
       <c r="H47" s="110" t="s">
         <v>235</v>
       </c>
       <c r="I47" s="110"/>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:9">
       <c r="H48" s="68" t="s">
         <v>236</v>
       </c>
       <c r="I48" s="110"/>
     </row>
-    <row r="49" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="8:9">
       <c r="H49" s="107" t="s">
         <v>237</v>
       </c>
       <c r="I49" s="110"/>
     </row>
-    <row r="50" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="8:9">
       <c r="H50" s="68" t="s">
         <v>238</v>
       </c>
       <c r="I50" s="110"/>
     </row>
-    <row r="51" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="8:9">
       <c r="H51" s="67" t="s">
         <v>239</v>
       </c>
       <c r="I51" s="110"/>
     </row>
-    <row r="52" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="8:9">
       <c r="H52" s="110" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="53" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="8:9">
       <c r="H53" s="107" t="s">
         <v>241</v>
       </c>
       <c r="I53" s="110"/>
     </row>
-    <row r="54" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="8:9">
       <c r="H54" s="67" t="s">
         <v>242</v>
       </c>
       <c r="I54" s="109"/>
     </row>
-    <row r="55" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="8:9">
       <c r="H55" s="68" t="s">
         <v>243</v>
       </c>
       <c r="I55" s="109"/>
     </row>
-    <row r="56" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="8:9">
       <c r="H56" s="107" t="s">
         <v>244</v>
       </c>
       <c r="I56" s="68"/>
     </row>
-    <row r="57" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="8:9">
       <c r="H57" s="68" t="s">
         <v>245</v>
       </c>
       <c r="I57" s="110"/>
     </row>
-    <row r="58" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="8:9">
       <c r="H58" s="68" t="s">
         <v>246</v>
       </c>
       <c r="I58" s="110"/>
     </row>
-    <row r="59" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="8:9">
       <c r="H59" s="110" t="s">
         <v>247</v>
       </c>
       <c r="I59" s="113"/>
     </row>
-    <row r="60" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="8:9">
       <c r="H60" s="113" t="s">
         <v>248</v>
       </c>
       <c r="I60" s="67"/>
     </row>
-    <row r="61" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="8:9">
       <c r="H61" s="67" t="s">
         <v>249</v>
       </c>
       <c r="I61" s="108"/>
     </row>
-    <row r="62" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="8:9">
       <c r="H62" s="67" t="s">
         <v>250</v>
       </c>
       <c r="I62" s="67"/>
     </row>
-    <row r="63" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="8:9">
       <c r="H63" s="108" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="64" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="8:9">
       <c r="H64" s="118" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="8:8">
       <c r="H65" s="109"/>
     </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="8:8">
       <c r="H66" s="107"/>
     </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="8:8">
       <c r="H67" s="110"/>
     </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="8:8">
       <c r="H68" s="100"/>
     </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="8:8">
       <c r="H69" s="110"/>
     </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="8:8">
       <c r="H70" s="68"/>
     </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="8:8">
       <c r="H71" s="107"/>
     </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="8:8">
       <c r="H72" s="109"/>
     </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="8:8">
       <c r="H73" s="98"/>
     </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="8:8">
       <c r="H74" s="105"/>
     </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="8:8">
       <c r="H75" s="114"/>
     </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="8:8">
       <c r="H76" s="114"/>
     </row>
   </sheetData>
@@ -10405,6 +10405,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -10542,54 +10557,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56CB4979-3D03-41A9-B345-AA2921FBC33F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CCB3A2F-2C86-4C8D-B7EA-4B3F9EF9489F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B705FE34-D5A2-4BFE-9004-2E123A88A3A8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B705FE34-D5A2-4BFE-9004-2E123A88A3A8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CCB3A2F-2C86-4C8D-B7EA-4B3F9EF9489F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56CB4979-3D03-41A9-B345-AA2921FBC33F}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
